--- a/Data/2015_F013B4_CO_ISOS/2015_F013B4_CO_ISOS_CropCanopy.xlsx
+++ b/Data/2015_F013B4_CO_ISOS/2015_F013B4_CO_ISOS_CropCanopy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2015_F013B4_CO_ISOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC1DA50-DABE-4138-9D16-4716D7A1AD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF24D96-9DA7-4CDD-81FA-11FBD1F7647E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1665" yWindow="-28410" windowWidth="18105" windowHeight="16065" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16200" yWindow="-28725" windowWidth="18105" windowHeight="14355" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Height" sheetId="11" r:id="rId1"/>
@@ -2242,18 +2242,6 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2263,7 +2251,16 @@
     <xf numFmtId="15" fontId="18" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2276,10 +2273,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2288,8 +2285,11 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2299,6 +2299,22 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="15" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2312,22 +2328,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -11036,6 +11036,10 @@
         <f>AVERAGE(F8:H11)/1.5</f>
         <v>11.222222222222221</v>
       </c>
+      <c r="L8" s="81">
+        <f>AVERAGE(F8:H11)/(1.5*1.016)</f>
+        <v>11.045494313210847</v>
+      </c>
       <c r="N8" s="114" t="s">
         <v>153</v>
       </c>
@@ -11062,6 +11066,7 @@
       <c r="H9" s="95">
         <v>18</v>
       </c>
+      <c r="L9" s="81"/>
       <c r="N9" s="114" t="s">
         <v>152</v>
       </c>
@@ -11082,6 +11087,7 @@
       <c r="H10" s="95">
         <v>17</v>
       </c>
+      <c r="L10" s="81"/>
     </row>
     <row r="11" spans="1:15" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="94"/>
@@ -11099,6 +11105,7 @@
       <c r="H11" s="92">
         <v>18</v>
       </c>
+      <c r="L11" s="81"/>
     </row>
     <row r="12" spans="1:15" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B12" s="105" t="s">
@@ -11129,6 +11136,10 @@
       <c r="K12" s="101">
         <f>AVERAGE(F12:H15)/1.5</f>
         <v>10.944444444444445</v>
+      </c>
+      <c r="L12" s="81">
+        <f>AVERAGE(F12:H15)/(1.5*1.016)</f>
+        <v>10.772090988626422</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -11149,6 +11160,7 @@
       <c r="H13" s="95">
         <v>16</v>
       </c>
+      <c r="L13" s="81"/>
     </row>
     <row r="14" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="99"/>
@@ -11166,6 +11178,7 @@
       <c r="H14" s="95">
         <v>17</v>
       </c>
+      <c r="L14" s="81"/>
     </row>
     <row r="15" spans="1:15" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="94"/>
@@ -11183,6 +11196,7 @@
       <c r="H15" s="92">
         <v>15</v>
       </c>
+      <c r="L15" s="81"/>
     </row>
     <row r="16" spans="1:15" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B16" s="109" t="s">
@@ -11214,8 +11228,12 @@
         <f>AVERAGE(F16:H19)/1.5</f>
         <v>10.111111111111111</v>
       </c>
-    </row>
-    <row r="17" spans="2:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L16" s="81">
+        <f>AVERAGE(F16:H19)/(1.5*1.016)</f>
+        <v>9.9518810148731411</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="112">
         <v>42151</v>
       </c>
@@ -11233,8 +11251,9 @@
       <c r="H17" s="95">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="2:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L17" s="81"/>
+    </row>
+    <row r="18" spans="2:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="106"/>
       <c r="C18" s="106"/>
       <c r="D18" s="106"/>
@@ -11250,8 +11269,9 @@
       <c r="H18" s="95">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="2:11" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L18" s="81"/>
+    </row>
+    <row r="19" spans="2:12" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="106"/>
       <c r="C19" s="106"/>
       <c r="D19" s="106"/>
@@ -11267,8 +11287,9 @@
       <c r="H19" s="92">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="2:11" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="L19" s="81"/>
+    </row>
+    <row r="20" spans="2:12" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B20" s="109" t="s">
         <v>2</v>
       </c>
@@ -11298,8 +11319,12 @@
         <f>AVERAGE(F20:H23)/1.5</f>
         <v>10.222222222222223</v>
       </c>
-    </row>
-    <row r="21" spans="2:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L20" s="81">
+        <f>AVERAGE(F20:H23)/(1.5*1.016)</f>
+        <v>10.061242344706912</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="112">
         <v>42151</v>
       </c>
@@ -11317,8 +11342,9 @@
       <c r="H21" s="95">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="2:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L21" s="81"/>
+    </row>
+    <row r="22" spans="2:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="106"/>
       <c r="C22" s="106"/>
       <c r="D22" s="106"/>
@@ -11334,8 +11360,9 @@
       <c r="H22" s="95">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="2:11" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L22" s="81"/>
+    </row>
+    <row r="23" spans="2:12" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="106"/>
       <c r="C23" s="106"/>
       <c r="D23" s="106"/>
@@ -11351,8 +11378,9 @@
       <c r="H23" s="92">
         <v>16</v>
       </c>
-    </row>
-    <row r="24" spans="2:11" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="L23" s="81"/>
+    </row>
+    <row r="24" spans="2:12" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B24" s="105" t="s">
         <v>2</v>
       </c>
@@ -11382,8 +11410,12 @@
         <f>AVERAGE(F24:H27)/1.5</f>
         <v>9.9444444444444446</v>
       </c>
-    </row>
-    <row r="25" spans="2:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L24" s="81">
+        <f>AVERAGE(F24:H27)/(1.5*1.016)</f>
+        <v>9.787839020122485</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="112">
         <v>42151</v>
       </c>
@@ -11401,8 +11433,9 @@
       <c r="H25" s="95">
         <v>17</v>
       </c>
-    </row>
-    <row r="26" spans="2:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L25" s="81"/>
+    </row>
+    <row r="26" spans="2:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="99"/>
       <c r="C26" s="99"/>
       <c r="D26" s="94"/>
@@ -11418,8 +11451,9 @@
       <c r="H26" s="95">
         <v>14</v>
       </c>
-    </row>
-    <row r="27" spans="2:11" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L26" s="81"/>
+    </row>
+    <row r="27" spans="2:12" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="94"/>
       <c r="C27" s="94"/>
       <c r="D27" s="94"/>
@@ -11435,8 +11469,9 @@
       <c r="H27" s="92">
         <v>13</v>
       </c>
-    </row>
-    <row r="28" spans="2:11" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="L27" s="81"/>
+    </row>
+    <row r="28" spans="2:12" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B28" s="105" t="s">
         <v>3</v>
       </c>
@@ -11466,8 +11501,12 @@
         <f>AVERAGE(F28:H31)/1.5</f>
         <v>10.277777777777777</v>
       </c>
-    </row>
-    <row r="29" spans="2:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L28" s="81">
+        <f>AVERAGE(F28:H31)/(1.5*1.016)</f>
+        <v>10.115923009623797</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="100">
         <v>42150</v>
       </c>
@@ -11485,8 +11524,9 @@
       <c r="H29" s="95">
         <v>19</v>
       </c>
-    </row>
-    <row r="30" spans="2:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L29" s="81"/>
+    </row>
+    <row r="30" spans="2:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="94"/>
       <c r="C30" s="94"/>
       <c r="D30" s="94"/>
@@ -11502,8 +11542,9 @@
       <c r="H30" s="111">
         <v>16</v>
       </c>
-    </row>
-    <row r="31" spans="2:11" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L30" s="81"/>
+    </row>
+    <row r="31" spans="2:12" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="94"/>
       <c r="C31" s="94"/>
       <c r="D31" s="94"/>
@@ -11519,8 +11560,9 @@
       <c r="H31" s="92">
         <v>17</v>
       </c>
-    </row>
-    <row r="32" spans="2:11" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="L31" s="81"/>
+    </row>
+    <row r="32" spans="2:12" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B32" s="109" t="s">
         <v>3</v>
       </c>
@@ -11549,6 +11591,10 @@
       <c r="K32" s="101">
         <f>AVERAGE(F32:H35)/1.5</f>
         <v>10.777777777777779</v>
+      </c>
+      <c r="L32" s="81">
+        <f>AVERAGE(F32:H35)/(1.5*1.016)</f>
+        <v>10.608048993875766</v>
       </c>
     </row>
     <row r="33" spans="2:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -11569,6 +11615,7 @@
       <c r="H33" s="95">
         <v>17</v>
       </c>
+      <c r="L33" s="81"/>
     </row>
     <row r="34" spans="2:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="106"/>
@@ -11586,6 +11633,7 @@
       <c r="H34" s="95">
         <v>16</v>
       </c>
+      <c r="L34" s="81"/>
     </row>
     <row r="35" spans="2:12" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="106"/>
@@ -11603,6 +11651,7 @@
       <c r="H35" s="92">
         <v>17</v>
       </c>
+      <c r="L35" s="81"/>
     </row>
     <row r="36" spans="2:12" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B36" s="109" t="s">
@@ -11633,6 +11682,10 @@
       <c r="K36" s="101">
         <f>AVERAGE(F36:H39)/1.5</f>
         <v>9.6111111111111107</v>
+      </c>
+      <c r="L36" s="81">
+        <f>AVERAGE(F36:H39)/(1.5*1.016)</f>
+        <v>9.4597550306211726</v>
       </c>
     </row>
     <row r="37" spans="2:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -11654,6 +11707,7 @@
         <v>14</v>
       </c>
       <c r="J37" s="107"/>
+      <c r="L37" s="81"/>
     </row>
     <row r="38" spans="2:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="106"/>
@@ -11671,6 +11725,7 @@
       <c r="H38" s="95">
         <v>15</v>
       </c>
+      <c r="L38" s="81"/>
     </row>
     <row r="39" spans="2:12" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="106"/>
@@ -11688,6 +11743,7 @@
       <c r="H39" s="92">
         <v>15</v>
       </c>
+      <c r="L39" s="81"/>
     </row>
     <row r="40" spans="2:12" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B40" s="105" t="s">
@@ -11718,6 +11774,10 @@
       <c r="K40" s="101">
         <f>AVERAGE(F40:H43)/1.5</f>
         <v>9.7777777777777768</v>
+      </c>
+      <c r="L40" s="81">
+        <f>AVERAGE(F40:H43)/(1.5*1.016)</f>
+        <v>9.6237970253718288</v>
       </c>
     </row>
     <row r="41" spans="2:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -11738,6 +11798,7 @@
       <c r="H41" s="95">
         <v>16</v>
       </c>
+      <c r="L41" s="81"/>
     </row>
     <row r="42" spans="2:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="94"/>
@@ -11755,6 +11816,7 @@
       <c r="H42" s="95">
         <v>15</v>
       </c>
+      <c r="L42" s="81"/>
     </row>
     <row r="43" spans="2:12" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="94"/>
@@ -11772,6 +11834,7 @@
       <c r="H43" s="92">
         <v>18</v>
       </c>
+      <c r="L43" s="81"/>
     </row>
     <row r="44" spans="2:12" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B44" s="105" t="s">
@@ -11802,6 +11865,10 @@
       <c r="K44" s="101">
         <f>AVERAGE(F44:H47)/1.5</f>
         <v>8.7777777777777768</v>
+      </c>
+      <c r="L44" s="81">
+        <f>AVERAGE(F44:H47)/(1.5*1.016)</f>
+        <v>8.6395450568678918</v>
       </c>
     </row>
     <row r="45" spans="2:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -11822,6 +11889,7 @@
       <c r="H45" s="97">
         <v>13</v>
       </c>
+      <c r="L45" s="81"/>
     </row>
     <row r="46" spans="2:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="94"/>
@@ -11839,6 +11907,7 @@
       <c r="H46" s="95">
         <v>14</v>
       </c>
+      <c r="L46" s="81"/>
     </row>
     <row r="47" spans="2:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="94"/>
@@ -11856,6 +11925,7 @@
       <c r="H47" s="92">
         <v>7</v>
       </c>
+      <c r="L47" s="81"/>
     </row>
     <row r="48" spans="2:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="91"/>
@@ -11869,7 +11939,7 @@
         <f>AVERAGE(K44,K40,K36,K32,K28,K24,K20,K16,K12,K8)</f>
         <v>10.166666666666666</v>
       </c>
-      <c r="L48">
+      <c r="L48" s="81">
         <f>K48/1.02</f>
         <v>9.9673202614379086</v>
       </c>
@@ -15073,75 +15143,75 @@
       <c r="D6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="182">
+      <c r="E6" s="180">
         <v>42192</v>
       </c>
-      <c r="F6" s="183"/>
-      <c r="G6" s="177">
+      <c r="F6" s="181"/>
+      <c r="G6" s="183">
         <v>42198</v>
       </c>
-      <c r="H6" s="178"/>
-      <c r="I6" s="182">
+      <c r="H6" s="184"/>
+      <c r="I6" s="180">
         <v>42207</v>
       </c>
-      <c r="J6" s="183"/>
-      <c r="K6" s="177">
+      <c r="J6" s="181"/>
+      <c r="K6" s="183">
         <v>42212</v>
       </c>
-      <c r="L6" s="178"/>
-      <c r="M6" s="177">
+      <c r="L6" s="184"/>
+      <c r="M6" s="183">
         <v>42219</v>
       </c>
-      <c r="N6" s="178"/>
-      <c r="O6" s="177">
+      <c r="N6" s="184"/>
+      <c r="O6" s="183">
         <v>42227</v>
       </c>
-      <c r="P6" s="178"/>
-      <c r="Q6" s="177">
+      <c r="P6" s="184"/>
+      <c r="Q6" s="183">
         <v>42240</v>
       </c>
-      <c r="R6" s="178"/>
-      <c r="S6" s="177">
+      <c r="R6" s="184"/>
+      <c r="S6" s="183">
         <v>42255</v>
       </c>
-      <c r="T6" s="178"/>
+      <c r="T6" s="184"/>
     </row>
     <row r="7" spans="1:29" ht="15" x14ac:dyDescent="0.25">
       <c r="D7" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="184">
+      <c r="E7" s="182">
         <v>188</v>
       </c>
-      <c r="F7" s="183"/>
-      <c r="G7" s="179">
+      <c r="F7" s="181"/>
+      <c r="G7" s="185">
         <v>194</v>
       </c>
-      <c r="H7" s="178"/>
-      <c r="I7" s="184">
+      <c r="H7" s="184"/>
+      <c r="I7" s="182">
         <v>203</v>
       </c>
-      <c r="J7" s="183"/>
-      <c r="K7" s="179">
+      <c r="J7" s="181"/>
+      <c r="K7" s="185">
         <v>208</v>
       </c>
-      <c r="L7" s="178"/>
-      <c r="M7" s="179">
+      <c r="L7" s="184"/>
+      <c r="M7" s="185">
         <v>215</v>
       </c>
-      <c r="N7" s="178"/>
-      <c r="O7" s="179">
+      <c r="N7" s="184"/>
+      <c r="O7" s="185">
         <v>223</v>
       </c>
-      <c r="P7" s="178"/>
-      <c r="Q7" s="179">
+      <c r="P7" s="184"/>
+      <c r="Q7" s="185">
         <v>236</v>
       </c>
-      <c r="R7" s="178"/>
-      <c r="S7" s="179">
+      <c r="R7" s="184"/>
+      <c r="S7" s="185">
         <v>251</v>
       </c>
-      <c r="T7" s="178"/>
+      <c r="T7" s="184"/>
     </row>
     <row r="8" spans="1:29" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D8" s="10"/>
@@ -15169,14 +15239,14 @@
         <v>221</v>
       </c>
       <c r="P8" s="153"/>
-      <c r="Q8" s="180" t="s">
+      <c r="Q8" s="186" t="s">
         <v>221</v>
       </c>
-      <c r="R8" s="181"/>
-      <c r="S8" s="180" t="s">
+      <c r="R8" s="187"/>
+      <c r="S8" s="186" t="s">
         <v>221</v>
       </c>
-      <c r="T8" s="181"/>
+      <c r="T8" s="187"/>
       <c r="V8" s="82" t="s">
         <v>220</v>
       </c>
@@ -19177,89 +19247,95 @@
       </c>
     </row>
     <row r="59" spans="2:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E59" s="185" t="s">
+      <c r="E59" s="177" t="s">
         <v>212</v>
       </c>
-      <c r="F59" s="186"/>
+      <c r="F59" s="178"/>
       <c r="G59" s="138"/>
-      <c r="I59" s="185" t="s">
+      <c r="I59" s="177" t="s">
         <v>212</v>
       </c>
-      <c r="J59" s="186"/>
-      <c r="O59" s="185" t="s">
+      <c r="J59" s="178"/>
+      <c r="O59" s="177" t="s">
         <v>211</v>
       </c>
-      <c r="P59" s="186"/>
-      <c r="Q59" s="185"/>
-      <c r="R59" s="186"/>
+      <c r="P59" s="178"/>
+      <c r="Q59" s="177"/>
+      <c r="R59" s="178"/>
     </row>
     <row r="60" spans="2:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E60" s="187"/>
-      <c r="F60" s="187"/>
+      <c r="E60" s="179"/>
+      <c r="F60" s="179"/>
       <c r="G60" s="138"/>
-      <c r="I60" s="187"/>
-      <c r="J60" s="187"/>
-      <c r="O60" s="187"/>
-      <c r="P60" s="187"/>
-      <c r="Q60" s="187"/>
-      <c r="R60" s="187"/>
+      <c r="I60" s="179"/>
+      <c r="J60" s="179"/>
+      <c r="O60" s="179"/>
+      <c r="P60" s="179"/>
+      <c r="Q60" s="179"/>
+      <c r="R60" s="179"/>
     </row>
     <row r="61" spans="2:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E61" s="187"/>
-      <c r="F61" s="187"/>
+      <c r="E61" s="179"/>
+      <c r="F61" s="179"/>
       <c r="G61" s="138"/>
-      <c r="I61" s="187"/>
-      <c r="J61" s="187"/>
-      <c r="O61" s="187"/>
-      <c r="P61" s="187"/>
-      <c r="Q61" s="187"/>
-      <c r="R61" s="187"/>
+      <c r="I61" s="179"/>
+      <c r="J61" s="179"/>
+      <c r="O61" s="179"/>
+      <c r="P61" s="179"/>
+      <c r="Q61" s="179"/>
+      <c r="R61" s="179"/>
     </row>
     <row r="62" spans="2:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E62" s="187"/>
-      <c r="F62" s="187"/>
+      <c r="E62" s="179"/>
+      <c r="F62" s="179"/>
       <c r="G62" s="138"/>
-      <c r="I62" s="187"/>
-      <c r="J62" s="187"/>
-      <c r="O62" s="187"/>
-      <c r="P62" s="187"/>
-      <c r="Q62" s="187"/>
-      <c r="R62" s="187"/>
+      <c r="I62" s="179"/>
+      <c r="J62" s="179"/>
+      <c r="O62" s="179"/>
+      <c r="P62" s="179"/>
+      <c r="Q62" s="179"/>
+      <c r="R62" s="179"/>
     </row>
     <row r="63" spans="2:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E63" s="166"/>
-      <c r="F63" s="166"/>
-      <c r="I63" s="166"/>
-      <c r="J63" s="166"/>
-      <c r="O63" s="166"/>
-      <c r="P63" s="166"/>
-      <c r="Q63" s="166"/>
-      <c r="R63" s="166"/>
+      <c r="E63" s="165"/>
+      <c r="F63" s="165"/>
+      <c r="I63" s="165"/>
+      <c r="J63" s="165"/>
+      <c r="O63" s="165"/>
+      <c r="P63" s="165"/>
+      <c r="Q63" s="165"/>
+      <c r="R63" s="165"/>
     </row>
     <row r="64" spans="2:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E64" s="166"/>
-      <c r="F64" s="166"/>
-      <c r="I64" s="166"/>
-      <c r="J64" s="166"/>
-      <c r="O64" s="166"/>
-      <c r="P64" s="166"/>
-      <c r="Q64" s="166"/>
-      <c r="R64" s="166"/>
+      <c r="E64" s="165"/>
+      <c r="F64" s="165"/>
+      <c r="I64" s="165"/>
+      <c r="J64" s="165"/>
+      <c r="O64" s="165"/>
+      <c r="P64" s="165"/>
+      <c r="Q64" s="165"/>
+      <c r="R64" s="165"/>
     </row>
     <row r="65" spans="15:18" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="O65" s="166"/>
-      <c r="P65" s="166"/>
-      <c r="Q65" s="166"/>
-      <c r="R65" s="166"/>
+      <c r="O65" s="165"/>
+      <c r="P65" s="165"/>
+      <c r="Q65" s="165"/>
+      <c r="R65" s="165"/>
     </row>
     <row r="66" spans="15:18" x14ac:dyDescent="0.2">
-      <c r="O66" s="166"/>
-      <c r="P66" s="166"/>
-      <c r="Q66" s="166"/>
-      <c r="R66" s="166"/>
+      <c r="O66" s="165"/>
+      <c r="P66" s="165"/>
+      <c r="Q66" s="165"/>
+      <c r="R66" s="165"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="S8:T8"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="Q7:R7"/>
     <mergeCell ref="Q59:R66"/>
     <mergeCell ref="O59:P66"/>
     <mergeCell ref="E6:F6"/>
@@ -19276,12 +19352,6 @@
     <mergeCell ref="M7:N7"/>
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="I7:J7"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="S8:T8"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="Q7:R7"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0.3"/>
   <pageSetup scale="69" fitToHeight="2" orientation="portrait" r:id="rId1"/>
@@ -25732,59 +25802,59 @@
       <c r="C5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="O5" s="161"/>
-      <c r="P5" s="162"/>
+      <c r="O5" s="157"/>
+      <c r="P5" s="158"/>
     </row>
     <row r="6" spans="1:28" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E6" s="165" t="s">
+      <c r="E6" s="164" t="s">
         <v>58</v>
       </c>
-      <c r="F6" s="166"/>
-      <c r="O6" s="162"/>
-      <c r="P6" s="162"/>
+      <c r="F6" s="165"/>
+      <c r="O6" s="158"/>
+      <c r="P6" s="158"/>
     </row>
     <row r="7" spans="1:28" ht="15" x14ac:dyDescent="0.25">
       <c r="D7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="163">
+      <c r="E7" s="159">
         <v>42157</v>
       </c>
-      <c r="F7" s="158"/>
-      <c r="G7" s="167">
+      <c r="F7" s="160"/>
+      <c r="G7" s="166">
         <v>42170</v>
       </c>
-      <c r="H7" s="168"/>
-      <c r="I7" s="159">
+      <c r="H7" s="167"/>
+      <c r="I7" s="162">
         <v>42184</v>
       </c>
-      <c r="J7" s="158"/>
-      <c r="K7" s="159">
+      <c r="J7" s="160"/>
+      <c r="K7" s="162">
         <v>42198</v>
       </c>
-      <c r="L7" s="158"/>
-      <c r="M7" s="159">
+      <c r="L7" s="160"/>
+      <c r="M7" s="162">
         <v>42212</v>
       </c>
-      <c r="N7" s="158"/>
-      <c r="O7" s="159">
+      <c r="N7" s="160"/>
+      <c r="O7" s="162">
         <v>42227</v>
       </c>
-      <c r="P7" s="158"/>
-      <c r="Q7" s="159">
+      <c r="P7" s="160"/>
+      <c r="Q7" s="162">
         <v>42243</v>
       </c>
-      <c r="R7" s="158"/>
-      <c r="S7" s="159">
+      <c r="R7" s="160"/>
+      <c r="S7" s="162">
         <v>42255</v>
       </c>
-      <c r="T7" s="158"/>
-      <c r="U7" s="157"/>
-      <c r="V7" s="158"/>
-      <c r="W7" s="157"/>
-      <c r="X7" s="158"/>
-      <c r="Y7" s="157"/>
-      <c r="Z7" s="158"/>
+      <c r="T7" s="160"/>
+      <c r="U7" s="168"/>
+      <c r="V7" s="160"/>
+      <c r="W7" s="168"/>
+      <c r="X7" s="160"/>
+      <c r="Y7" s="168"/>
+      <c r="Z7" s="160"/>
       <c r="AA7" s="29"/>
       <c r="AB7" s="29"/>
     </row>
@@ -25792,44 +25862,44 @@
       <c r="D8" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="164">
+      <c r="E8" s="161">
         <v>153</v>
       </c>
-      <c r="F8" s="158"/>
+      <c r="F8" s="160"/>
       <c r="G8" s="64">
         <v>166</v>
       </c>
       <c r="H8" s="64"/>
-      <c r="I8" s="157">
+      <c r="I8" s="168">
         <v>180</v>
       </c>
-      <c r="J8" s="158"/>
-      <c r="K8" s="160">
+      <c r="J8" s="160"/>
+      <c r="K8" s="163">
         <v>194</v>
       </c>
-      <c r="L8" s="158"/>
-      <c r="M8" s="160">
+      <c r="L8" s="160"/>
+      <c r="M8" s="163">
         <v>208</v>
       </c>
-      <c r="N8" s="158"/>
-      <c r="O8" s="160">
+      <c r="N8" s="160"/>
+      <c r="O8" s="163">
         <v>223</v>
       </c>
-      <c r="P8" s="158"/>
-      <c r="Q8" s="160">
+      <c r="P8" s="160"/>
+      <c r="Q8" s="163">
         <v>236</v>
       </c>
-      <c r="R8" s="158"/>
-      <c r="S8" s="160">
+      <c r="R8" s="160"/>
+      <c r="S8" s="163">
         <v>251</v>
       </c>
-      <c r="T8" s="158"/>
-      <c r="U8" s="157"/>
-      <c r="V8" s="158"/>
-      <c r="W8" s="157"/>
-      <c r="X8" s="158"/>
-      <c r="Y8" s="157"/>
-      <c r="Z8" s="158"/>
+      <c r="T8" s="160"/>
+      <c r="U8" s="168"/>
+      <c r="V8" s="160"/>
+      <c r="W8" s="168"/>
+      <c r="X8" s="160"/>
+      <c r="Y8" s="168"/>
+      <c r="Z8" s="160"/>
       <c r="AA8" s="29"/>
       <c r="AB8" s="29"/>
     </row>
@@ -29316,6 +29386,16 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="W7:X7"/>
+    <mergeCell ref="W8:X8"/>
+    <mergeCell ref="Y7:Z7"/>
+    <mergeCell ref="Y8:Z8"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="S8:T8"/>
+    <mergeCell ref="U7:V7"/>
+    <mergeCell ref="U8:V8"/>
     <mergeCell ref="O5:P6"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E8:F8"/>
@@ -29329,16 +29409,6 @@
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="I8:J8"/>
-    <mergeCell ref="W7:X7"/>
-    <mergeCell ref="W8:X8"/>
-    <mergeCell ref="Y7:Z7"/>
-    <mergeCell ref="Y8:Z8"/>
-    <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="S8:T8"/>
-    <mergeCell ref="U7:V7"/>
-    <mergeCell ref="U8:V8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -29381,7 +29451,7 @@
       <c r="O3" s="155" t="s">
         <v>62</v>
       </c>
-      <c r="P3" s="169"/>
+      <c r="P3" s="173"/>
     </row>
     <row r="4" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
@@ -29389,7 +29459,7 @@
       </c>
       <c r="C4" s="4"/>
       <c r="O4" s="156"/>
-      <c r="P4" s="169"/>
+      <c r="P4" s="173"/>
     </row>
     <row r="5" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="4"/>
@@ -29397,7 +29467,7 @@
         <v>44</v>
       </c>
       <c r="O5" s="156"/>
-      <c r="P5" s="169"/>
+      <c r="P5" s="173"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C6" s="65"/>
@@ -29405,7 +29475,7 @@
         <v>45</v>
       </c>
       <c r="O6" s="156"/>
-      <c r="P6" s="169"/>
+      <c r="P6" s="173"/>
     </row>
     <row r="7" spans="1:28" ht="15" x14ac:dyDescent="0.25">
       <c r="D7" s="10" t="s">
@@ -29414,43 +29484,43 @@
       <c r="E7" s="69">
         <v>42157</v>
       </c>
-      <c r="F7" s="171" t="s">
+      <c r="F7" s="170" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="159">
+      <c r="G7" s="162">
         <v>42170</v>
       </c>
-      <c r="H7" s="158"/>
-      <c r="I7" s="159">
+      <c r="H7" s="160"/>
+      <c r="I7" s="162">
         <v>42184</v>
       </c>
-      <c r="J7" s="170"/>
-      <c r="K7" s="159">
+      <c r="J7" s="172"/>
+      <c r="K7" s="162">
         <v>42198</v>
       </c>
-      <c r="L7" s="170"/>
-      <c r="M7" s="159">
+      <c r="L7" s="172"/>
+      <c r="M7" s="162">
         <v>42212</v>
       </c>
-      <c r="N7" s="158"/>
-      <c r="O7" s="159">
+      <c r="N7" s="160"/>
+      <c r="O7" s="162">
         <v>42227</v>
       </c>
-      <c r="P7" s="158"/>
-      <c r="Q7" s="159">
+      <c r="P7" s="160"/>
+      <c r="Q7" s="162">
         <v>42243</v>
       </c>
-      <c r="R7" s="158"/>
-      <c r="S7" s="159">
+      <c r="R7" s="160"/>
+      <c r="S7" s="162">
         <v>42255</v>
       </c>
-      <c r="T7" s="158"/>
-      <c r="U7" s="157"/>
-      <c r="V7" s="158"/>
-      <c r="W7" s="157"/>
-      <c r="X7" s="158"/>
-      <c r="Y7" s="157"/>
-      <c r="Z7" s="158"/>
+      <c r="T7" s="160"/>
+      <c r="U7" s="168"/>
+      <c r="V7" s="160"/>
+      <c r="W7" s="168"/>
+      <c r="X7" s="160"/>
+      <c r="Y7" s="168"/>
+      <c r="Z7" s="160"/>
       <c r="AA7" s="29"/>
       <c r="AB7" s="29"/>
     </row>
@@ -29461,41 +29531,41 @@
       <c r="E8" s="33">
         <v>153</v>
       </c>
-      <c r="F8" s="172"/>
-      <c r="G8" s="157">
+      <c r="F8" s="171"/>
+      <c r="G8" s="168">
         <v>166</v>
       </c>
-      <c r="H8" s="158"/>
-      <c r="I8" s="157">
+      <c r="H8" s="160"/>
+      <c r="I8" s="168">
         <v>180</v>
       </c>
-      <c r="J8" s="173"/>
-      <c r="K8" s="157">
+      <c r="J8" s="169"/>
+      <c r="K8" s="168">
         <v>194</v>
       </c>
-      <c r="L8" s="173"/>
-      <c r="M8" s="160">
+      <c r="L8" s="169"/>
+      <c r="M8" s="163">
         <v>208</v>
       </c>
-      <c r="N8" s="158"/>
-      <c r="O8" s="160">
+      <c r="N8" s="160"/>
+      <c r="O8" s="163">
         <v>223</v>
       </c>
-      <c r="P8" s="158"/>
-      <c r="Q8" s="160">
+      <c r="P8" s="160"/>
+      <c r="Q8" s="163">
         <v>236</v>
       </c>
-      <c r="R8" s="158"/>
-      <c r="S8" s="160">
+      <c r="R8" s="160"/>
+      <c r="S8" s="163">
         <v>251</v>
       </c>
-      <c r="T8" s="158"/>
-      <c r="U8" s="157"/>
-      <c r="V8" s="158"/>
-      <c r="W8" s="157"/>
-      <c r="X8" s="158"/>
-      <c r="Y8" s="157"/>
-      <c r="Z8" s="158"/>
+      <c r="T8" s="160"/>
+      <c r="U8" s="168"/>
+      <c r="V8" s="160"/>
+      <c r="W8" s="168"/>
+      <c r="X8" s="160"/>
+      <c r="Y8" s="168"/>
+      <c r="Z8" s="160"/>
       <c r="AA8" s="29"/>
       <c r="AB8" s="29"/>
     </row>
@@ -32559,37 +32629,37 @@
       <c r="E65" s="69">
         <v>42157</v>
       </c>
-      <c r="F65" s="171" t="s">
+      <c r="F65" s="170" t="s">
         <v>59</v>
       </c>
-      <c r="G65" s="159">
+      <c r="G65" s="162">
         <v>42170</v>
       </c>
-      <c r="H65" s="158"/>
-      <c r="I65" s="159">
+      <c r="H65" s="160"/>
+      <c r="I65" s="162">
         <v>42184</v>
       </c>
-      <c r="J65" s="170"/>
-      <c r="K65" s="159">
+      <c r="J65" s="172"/>
+      <c r="K65" s="162">
         <v>42198</v>
       </c>
-      <c r="L65" s="170"/>
-      <c r="M65" s="159">
+      <c r="L65" s="172"/>
+      <c r="M65" s="162">
         <v>42212</v>
       </c>
-      <c r="N65" s="158"/>
-      <c r="O65" s="159">
+      <c r="N65" s="160"/>
+      <c r="O65" s="162">
         <v>42227</v>
       </c>
-      <c r="P65" s="158"/>
-      <c r="Q65" s="159">
+      <c r="P65" s="160"/>
+      <c r="Q65" s="162">
         <v>42243</v>
       </c>
-      <c r="R65" s="158"/>
-      <c r="S65" s="159">
+      <c r="R65" s="160"/>
+      <c r="S65" s="162">
         <v>42255</v>
       </c>
-      <c r="T65" s="158"/>
+      <c r="T65" s="160"/>
     </row>
     <row r="66" spans="4:20" ht="15" x14ac:dyDescent="0.25">
       <c r="D66" s="10" t="s">
@@ -32598,53 +32668,44 @@
       <c r="E66" s="33">
         <v>153</v>
       </c>
-      <c r="F66" s="172"/>
-      <c r="G66" s="157">
+      <c r="F66" s="171"/>
+      <c r="G66" s="168">
         <v>166</v>
       </c>
-      <c r="H66" s="158"/>
-      <c r="I66" s="157">
+      <c r="H66" s="160"/>
+      <c r="I66" s="168">
         <v>180</v>
       </c>
-      <c r="J66" s="173"/>
-      <c r="K66" s="157">
+      <c r="J66" s="169"/>
+      <c r="K66" s="168">
         <v>194</v>
       </c>
-      <c r="L66" s="173"/>
-      <c r="M66" s="160">
+      <c r="L66" s="169"/>
+      <c r="M66" s="163">
         <v>208</v>
       </c>
-      <c r="N66" s="158"/>
-      <c r="O66" s="160">
+      <c r="N66" s="160"/>
+      <c r="O66" s="163">
         <v>223</v>
       </c>
-      <c r="P66" s="158"/>
-      <c r="Q66" s="160">
+      <c r="P66" s="160"/>
+      <c r="Q66" s="163">
         <v>236</v>
       </c>
-      <c r="R66" s="158"/>
-      <c r="S66" s="160">
+      <c r="R66" s="160"/>
+      <c r="S66" s="163">
         <v>251</v>
       </c>
-      <c r="T66" s="158"/>
+      <c r="T66" s="160"/>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="O65:P65"/>
-    <mergeCell ref="Q65:R65"/>
-    <mergeCell ref="S65:T65"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="I66:J66"/>
-    <mergeCell ref="K66:L66"/>
-    <mergeCell ref="M66:N66"/>
-    <mergeCell ref="O66:P66"/>
-    <mergeCell ref="Q66:R66"/>
-    <mergeCell ref="S66:T66"/>
-    <mergeCell ref="F65:F66"/>
-    <mergeCell ref="G65:H65"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="O3:P6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M7:N7"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="Y8:Z8"/>
     <mergeCell ref="Q7:R7"/>
@@ -32661,12 +32722,21 @@
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="M8:N8"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="O3:P6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="O65:P65"/>
+    <mergeCell ref="Q65:R65"/>
+    <mergeCell ref="S65:T65"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="K66:L66"/>
+    <mergeCell ref="M66:N66"/>
+    <mergeCell ref="O66:P66"/>
+    <mergeCell ref="Q66:R66"/>
+    <mergeCell ref="S66:T66"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Data/2015_F013B4_CO_ISOS/2015_F013B4_CO_ISOS_CropCanopy.xlsx
+++ b/Data/2015_F013B4_CO_ISOS/2015_F013B4_CO_ISOS_CropCanopy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2015_F013B4_CO_ISOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF24D96-9DA7-4CDD-81FA-11FBD1F7647E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B03FD6D6-C4DF-4C59-89A0-53C2C5917AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16200" yWindow="-28725" windowWidth="18105" windowHeight="14355" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1755" yWindow="-23730" windowWidth="16335" windowHeight="23370" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Height" sheetId="11" r:id="rId1"/>
@@ -18,26 +18,27 @@
     <sheet name="LAImeter" sheetId="14" r:id="rId3"/>
     <sheet name="Density" sheetId="13" r:id="rId4"/>
     <sheet name="Develop" sheetId="16" r:id="rId5"/>
-    <sheet name="Summary-Plant Heights" sheetId="6" r:id="rId6"/>
-    <sheet name="Summary-Bed Heights" sheetId="7" r:id="rId7"/>
-    <sheet name="Summary-Cover" sheetId="8" r:id="rId8"/>
-    <sheet name="Blank" sheetId="4" r:id="rId9"/>
-    <sheet name="graphs" sheetId="10" r:id="rId10"/>
-    <sheet name="Emergence" sheetId="17" r:id="rId11"/>
-    <sheet name="1stLeaf" sheetId="18" r:id="rId12"/>
-    <sheet name="Density at flags" sheetId="9" r:id="rId13"/>
-    <sheet name="Density counts" sheetId="15" r:id="rId14"/>
-    <sheet name="Flowering" sheetId="19" r:id="rId15"/>
-    <sheet name="NAWF" sheetId="20" r:id="rId16"/>
+    <sheet name="PlotDevelop" sheetId="21" r:id="rId6"/>
+    <sheet name="Summary-Plant Heights" sheetId="6" r:id="rId7"/>
+    <sheet name="Summary-Bed Heights" sheetId="7" r:id="rId8"/>
+    <sheet name="Summary-Cover" sheetId="8" r:id="rId9"/>
+    <sheet name="Blank" sheetId="4" r:id="rId10"/>
+    <sheet name="graphs" sheetId="10" r:id="rId11"/>
+    <sheet name="Emergence" sheetId="17" r:id="rId12"/>
+    <sheet name="1stLeaf" sheetId="18" r:id="rId13"/>
+    <sheet name="Density at flags" sheetId="9" r:id="rId14"/>
+    <sheet name="Density counts" sheetId="15" r:id="rId15"/>
+    <sheet name="Flowering" sheetId="19" r:id="rId16"/>
+    <sheet name="NAWF" sheetId="20" r:id="rId17"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">Blank!$A$1:$V$19</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="13">'Density counts'!$A$1:$H$47</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="14">Flowering!$A$1:$L$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">NAWF!$A$1:$N$58</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">Blank!$8:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="13">'Density counts'!$6:$7</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="15">NAWF!$6:$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">Blank!$A$1:$V$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'Density counts'!$A$1:$H$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">Flowering!$A$1:$L$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">NAWF!$A$1:$N$58</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">Blank!$8:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'Density counts'!$6:$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="16">NAWF!$6:$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="240">
   <si>
     <t>Span 1</t>
   </si>
@@ -961,6 +962,51 @@
   <si>
     <t>ADAT</t>
   </si>
+  <si>
+    <t>Plot</t>
+  </si>
+  <si>
+    <t>p02</t>
+  </si>
+  <si>
+    <t>p03</t>
+  </si>
+  <si>
+    <t>p04</t>
+  </si>
+  <si>
+    <t>p05</t>
+  </si>
+  <si>
+    <t>p06</t>
+  </si>
+  <si>
+    <t>p07</t>
+  </si>
+  <si>
+    <t>p08</t>
+  </si>
+  <si>
+    <t>p09</t>
+  </si>
+  <si>
+    <t>p10</t>
+  </si>
+  <si>
+    <t>EDATE</t>
+  </si>
+  <si>
+    <t>PLYRE</t>
+  </si>
+  <si>
+    <t>PLDOE</t>
+  </si>
+  <si>
+    <t>LF1D</t>
+  </si>
+  <si>
+    <t>p11</t>
+  </si>
 </sst>
 </file>
 
@@ -972,7 +1018,7 @@
     <numFmt numFmtId="166" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="167" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="47" x14ac:knownFonts="1">
+  <fonts count="48" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1304,6 +1350,12 @@
       <color rgb="FF7030A0"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -2242,6 +2294,18 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2251,16 +2315,7 @@
     <xf numFmtId="15" fontId="18" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2273,10 +2328,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2285,11 +2340,8 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2299,6 +2351,19 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2315,19 +2380,6 @@
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -8284,6 +8336,697 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:V74"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.42578125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" style="6" customWidth="1"/>
+    <col min="3" max="4" width="9.7109375" style="6" customWidth="1"/>
+    <col min="5" max="22" width="9.7109375" style="5" customWidth="1"/>
+    <col min="23" max="24" width="8.7109375" style="5" customWidth="1"/>
+    <col min="25" max="16384" width="8.85546875" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="2">
+        <v>2015</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+    </row>
+    <row r="2" spans="1:22" ht="18" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+    </row>
+    <row r="3" spans="1:22" ht="18" x14ac:dyDescent="0.25">
+      <c r="B3" s="3"/>
+    </row>
+    <row r="4" spans="1:22" ht="27" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="9"/>
+      <c r="H4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="9"/>
+      <c r="L4" s="11"/>
+      <c r="P4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="H5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="12"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+    </row>
+    <row r="6" spans="1:22" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="J6" s="10"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+    </row>
+    <row r="7" spans="1:22" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="J7" s="10"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+    </row>
+    <row r="8" spans="1:22" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="C8" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="54"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="54"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="62"/>
+      <c r="K8" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="L8" s="54"/>
+      <c r="M8" s="61"/>
+      <c r="N8" s="62"/>
+      <c r="O8" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="P8" s="54"/>
+      <c r="Q8" s="61"/>
+      <c r="R8" s="62"/>
+      <c r="S8" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="T8" s="54"/>
+      <c r="U8" s="61"/>
+      <c r="V8" s="62"/>
+    </row>
+    <row r="9" spans="1:22" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="60" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="J9" s="60" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="N9" s="60" t="s">
+        <v>35</v>
+      </c>
+      <c r="O9" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="P9" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q9" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="R9" s="60" t="s">
+        <v>35</v>
+      </c>
+      <c r="S9" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="T9" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="U9" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="V9" s="60" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="58"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="59"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="58"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="59"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="58"/>
+      <c r="Q10" s="38"/>
+      <c r="R10" s="59"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="58"/>
+      <c r="U10" s="38"/>
+      <c r="V10" s="59"/>
+    </row>
+    <row r="11" spans="1:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="17"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="59"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="58"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="59"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="58"/>
+      <c r="Q11" s="38"/>
+      <c r="R11" s="59"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="58"/>
+      <c r="U11" s="38"/>
+      <c r="V11" s="59"/>
+    </row>
+    <row r="12" spans="1:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="17"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="58"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="59"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="58"/>
+      <c r="M12" s="38"/>
+      <c r="N12" s="59"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="58"/>
+      <c r="Q12" s="38"/>
+      <c r="R12" s="59"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="58"/>
+      <c r="U12" s="38"/>
+      <c r="V12" s="59"/>
+    </row>
+    <row r="13" spans="1:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="17"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="58"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="59"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="58"/>
+      <c r="M13" s="38"/>
+      <c r="N13" s="59"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="58"/>
+      <c r="Q13" s="38"/>
+      <c r="R13" s="59"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="58"/>
+      <c r="U13" s="38"/>
+      <c r="V13" s="59"/>
+    </row>
+    <row r="14" spans="1:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="17"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="58"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="59"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="58"/>
+      <c r="M14" s="38"/>
+      <c r="N14" s="59"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="58"/>
+      <c r="Q14" s="38"/>
+      <c r="R14" s="59"/>
+      <c r="S14" s="17"/>
+      <c r="T14" s="58"/>
+      <c r="U14" s="38"/>
+      <c r="V14" s="59"/>
+    </row>
+    <row r="15" spans="1:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="17"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="58"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="59"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="58"/>
+      <c r="M15" s="38"/>
+      <c r="N15" s="59"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="58"/>
+      <c r="Q15" s="38"/>
+      <c r="R15" s="59"/>
+      <c r="S15" s="17"/>
+      <c r="T15" s="58"/>
+      <c r="U15" s="38"/>
+      <c r="V15" s="59"/>
+    </row>
+    <row r="16" spans="1:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="17"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="59"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="58"/>
+      <c r="M16" s="38"/>
+      <c r="N16" s="59"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="58"/>
+      <c r="Q16" s="38"/>
+      <c r="R16" s="59"/>
+      <c r="S16" s="17"/>
+      <c r="T16" s="58"/>
+      <c r="U16" s="38"/>
+      <c r="V16" s="59"/>
+    </row>
+    <row r="17" spans="2:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="17"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="58"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="59"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="58"/>
+      <c r="M17" s="38"/>
+      <c r="N17" s="59"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="58"/>
+      <c r="Q17" s="38"/>
+      <c r="R17" s="59"/>
+      <c r="S17" s="17"/>
+      <c r="T17" s="58"/>
+      <c r="U17" s="38"/>
+      <c r="V17" s="59"/>
+    </row>
+    <row r="18" spans="2:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="17"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="59"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="58"/>
+      <c r="M18" s="38"/>
+      <c r="N18" s="59"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="58"/>
+      <c r="Q18" s="38"/>
+      <c r="R18" s="59"/>
+      <c r="S18" s="17"/>
+      <c r="T18" s="58"/>
+      <c r="U18" s="38"/>
+      <c r="V18" s="59"/>
+    </row>
+    <row r="19" spans="2:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="17"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="59"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="58"/>
+      <c r="M19" s="38"/>
+      <c r="N19" s="59"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="58"/>
+      <c r="Q19" s="38"/>
+      <c r="R19" s="59"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="58"/>
+      <c r="U19" s="38"/>
+      <c r="V19" s="59"/>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="G20" s="55"/>
+      <c r="H20" s="55"/>
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="G21" s="56"/>
+      <c r="H21" s="56"/>
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="G22" s="56"/>
+      <c r="H22" s="56"/>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="G23" s="56"/>
+      <c r="H23" s="56"/>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="G24" s="56"/>
+      <c r="H24" s="56"/>
+    </row>
+    <row r="25" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="G25" s="56"/>
+      <c r="H25" s="56"/>
+    </row>
+    <row r="26" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="G26" s="56"/>
+      <c r="H26" s="56"/>
+    </row>
+    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="G27" s="56"/>
+      <c r="H27" s="56"/>
+    </row>
+    <row r="28" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="G29" s="56"/>
+      <c r="H29" s="56"/>
+    </row>
+    <row r="30" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="G30" s="56"/>
+      <c r="H30" s="56"/>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="G31" s="56"/>
+      <c r="H31" s="56"/>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="G32" s="56"/>
+      <c r="H32" s="56"/>
+    </row>
+    <row r="33" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G33" s="56"/>
+      <c r="H33" s="56"/>
+    </row>
+    <row r="34" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G34" s="56"/>
+      <c r="H34" s="56"/>
+    </row>
+    <row r="35" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
+    </row>
+    <row r="36" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G36" s="56"/>
+      <c r="H36" s="56"/>
+    </row>
+    <row r="37" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G37" s="56"/>
+      <c r="H37" s="56"/>
+    </row>
+    <row r="38" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G38" s="56"/>
+      <c r="H38" s="56"/>
+    </row>
+    <row r="39" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G39" s="56"/>
+      <c r="H39" s="56"/>
+    </row>
+    <row r="40" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G40" s="56"/>
+      <c r="H40" s="56"/>
+    </row>
+    <row r="41" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G41" s="56"/>
+      <c r="H41" s="56"/>
+    </row>
+    <row r="42" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G42" s="56"/>
+      <c r="H42" s="56"/>
+    </row>
+    <row r="43" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G43" s="56"/>
+      <c r="H43" s="56"/>
+    </row>
+    <row r="44" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G44" s="56"/>
+      <c r="H44" s="56"/>
+    </row>
+    <row r="45" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G45" s="56"/>
+      <c r="H45" s="56"/>
+    </row>
+    <row r="46" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G46" s="56"/>
+      <c r="H46" s="56"/>
+    </row>
+    <row r="47" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G47" s="56"/>
+      <c r="H47" s="56"/>
+    </row>
+    <row r="48" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G48" s="56"/>
+      <c r="H48" s="56"/>
+    </row>
+    <row r="49" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G49" s="56"/>
+      <c r="H49" s="56"/>
+    </row>
+    <row r="50" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G50" s="56"/>
+      <c r="H50" s="56"/>
+    </row>
+    <row r="51" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G51" s="56"/>
+      <c r="H51" s="56"/>
+    </row>
+    <row r="52" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G52" s="56"/>
+      <c r="H52" s="56"/>
+    </row>
+    <row r="53" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G53" s="56"/>
+      <c r="H53" s="56"/>
+    </row>
+    <row r="54" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G54" s="56"/>
+      <c r="H54" s="56"/>
+    </row>
+    <row r="55" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G55" s="56"/>
+      <c r="H55" s="56"/>
+    </row>
+    <row r="56" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G56" s="56"/>
+      <c r="H56" s="56"/>
+    </row>
+    <row r="57" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G57" s="56"/>
+      <c r="H57" s="56"/>
+    </row>
+    <row r="58" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G58" s="56"/>
+      <c r="H58" s="56"/>
+    </row>
+    <row r="59" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G59" s="56"/>
+      <c r="H59" s="56"/>
+    </row>
+    <row r="60" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G60" s="56"/>
+      <c r="H60" s="56"/>
+    </row>
+    <row r="61" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G61" s="56"/>
+      <c r="H61" s="56"/>
+    </row>
+    <row r="62" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G62" s="56"/>
+      <c r="H62" s="56"/>
+    </row>
+    <row r="63" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G63" s="56"/>
+      <c r="H63" s="56"/>
+    </row>
+    <row r="64" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G64" s="56"/>
+      <c r="H64" s="56"/>
+    </row>
+    <row r="65" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G65" s="56"/>
+      <c r="H65" s="56"/>
+    </row>
+    <row r="66" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G66" s="56"/>
+      <c r="H66" s="56"/>
+    </row>
+    <row r="67" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G67" s="56"/>
+      <c r="H67" s="56"/>
+    </row>
+    <row r="68" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G68" s="56"/>
+      <c r="H68" s="56"/>
+    </row>
+    <row r="69" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G69" s="56"/>
+      <c r="H69" s="56"/>
+    </row>
+    <row r="70" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G70" s="56"/>
+      <c r="H70" s="56"/>
+    </row>
+    <row r="71" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G71" s="56"/>
+      <c r="H71" s="56"/>
+    </row>
+    <row r="72" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G72" s="56"/>
+      <c r="H72" s="56"/>
+    </row>
+    <row r="73" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G73" s="56"/>
+      <c r="H73" s="56"/>
+    </row>
+    <row r="74" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G74" s="56"/>
+      <c r="H74" s="56"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="1" header="0.3" footer="0.53"/>
+  <pageSetup scale="63" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;R&amp;Z&amp;F
+&amp;P of &amp;N
+smm</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:T14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9031,7 +9774,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D399F068-8A00-448C-B013-7CB7EF546F08}">
   <dimension ref="A1:N23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9569,7 +10312,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71E670D2-AEBC-4BBD-8B69-FC36645F2013}">
   <dimension ref="A1:N24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10094,7 +10837,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G59"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -10922,7 +11665,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30ABADD5-C32A-4868-8C2D-1D19989B2060}">
   <dimension ref="A1:O180"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12786,7 +13529,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E8E3F17-4CCB-4874-BDE2-10E677B6EB6C}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -15095,7 +15838,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{029F6F37-89EB-4681-8A31-9B0642227F83}">
   <dimension ref="A1:AC66"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -15143,75 +15886,75 @@
       <c r="D6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="180">
+      <c r="E6" s="185">
         <v>42192</v>
       </c>
-      <c r="F6" s="181"/>
-      <c r="G6" s="183">
+      <c r="F6" s="186"/>
+      <c r="G6" s="177">
         <v>42198</v>
       </c>
-      <c r="H6" s="184"/>
-      <c r="I6" s="180">
+      <c r="H6" s="178"/>
+      <c r="I6" s="185">
         <v>42207</v>
       </c>
-      <c r="J6" s="181"/>
-      <c r="K6" s="183">
+      <c r="J6" s="186"/>
+      <c r="K6" s="177">
         <v>42212</v>
       </c>
-      <c r="L6" s="184"/>
-      <c r="M6" s="183">
+      <c r="L6" s="178"/>
+      <c r="M6" s="177">
         <v>42219</v>
       </c>
-      <c r="N6" s="184"/>
-      <c r="O6" s="183">
+      <c r="N6" s="178"/>
+      <c r="O6" s="177">
         <v>42227</v>
       </c>
-      <c r="P6" s="184"/>
-      <c r="Q6" s="183">
+      <c r="P6" s="178"/>
+      <c r="Q6" s="177">
         <v>42240</v>
       </c>
-      <c r="R6" s="184"/>
-      <c r="S6" s="183">
+      <c r="R6" s="178"/>
+      <c r="S6" s="177">
         <v>42255</v>
       </c>
-      <c r="T6" s="184"/>
+      <c r="T6" s="178"/>
     </row>
     <row r="7" spans="1:29" ht="15" x14ac:dyDescent="0.25">
       <c r="D7" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="182">
+      <c r="E7" s="187">
         <v>188</v>
       </c>
-      <c r="F7" s="181"/>
-      <c r="G7" s="185">
+      <c r="F7" s="186"/>
+      <c r="G7" s="179">
         <v>194</v>
       </c>
-      <c r="H7" s="184"/>
-      <c r="I7" s="182">
+      <c r="H7" s="178"/>
+      <c r="I7" s="187">
         <v>203</v>
       </c>
-      <c r="J7" s="181"/>
-      <c r="K7" s="185">
+      <c r="J7" s="186"/>
+      <c r="K7" s="179">
         <v>208</v>
       </c>
-      <c r="L7" s="184"/>
-      <c r="M7" s="185">
+      <c r="L7" s="178"/>
+      <c r="M7" s="179">
         <v>215</v>
       </c>
-      <c r="N7" s="184"/>
-      <c r="O7" s="185">
+      <c r="N7" s="178"/>
+      <c r="O7" s="179">
         <v>223</v>
       </c>
-      <c r="P7" s="184"/>
-      <c r="Q7" s="185">
+      <c r="P7" s="178"/>
+      <c r="Q7" s="179">
         <v>236</v>
       </c>
-      <c r="R7" s="184"/>
-      <c r="S7" s="185">
+      <c r="R7" s="178"/>
+      <c r="S7" s="179">
         <v>251</v>
       </c>
-      <c r="T7" s="184"/>
+      <c r="T7" s="178"/>
     </row>
     <row r="8" spans="1:29" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D8" s="10"/>
@@ -15239,14 +15982,14 @@
         <v>221</v>
       </c>
       <c r="P8" s="153"/>
-      <c r="Q8" s="186" t="s">
+      <c r="Q8" s="180" t="s">
         <v>221</v>
       </c>
-      <c r="R8" s="187"/>
-      <c r="S8" s="186" t="s">
+      <c r="R8" s="181"/>
+      <c r="S8" s="180" t="s">
         <v>221</v>
       </c>
-      <c r="T8" s="187"/>
+      <c r="T8" s="181"/>
       <c r="V8" s="82" t="s">
         <v>220</v>
       </c>
@@ -19247,95 +19990,89 @@
       </c>
     </row>
     <row r="59" spans="2:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E59" s="177" t="s">
+      <c r="E59" s="182" t="s">
         <v>212</v>
       </c>
-      <c r="F59" s="178"/>
+      <c r="F59" s="183"/>
       <c r="G59" s="138"/>
-      <c r="I59" s="177" t="s">
+      <c r="I59" s="182" t="s">
         <v>212</v>
       </c>
-      <c r="J59" s="178"/>
-      <c r="O59" s="177" t="s">
+      <c r="J59" s="183"/>
+      <c r="O59" s="182" t="s">
         <v>211</v>
       </c>
-      <c r="P59" s="178"/>
-      <c r="Q59" s="177"/>
-      <c r="R59" s="178"/>
+      <c r="P59" s="183"/>
+      <c r="Q59" s="182"/>
+      <c r="R59" s="183"/>
     </row>
     <row r="60" spans="2:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E60" s="179"/>
-      <c r="F60" s="179"/>
+      <c r="E60" s="184"/>
+      <c r="F60" s="184"/>
       <c r="G60" s="138"/>
-      <c r="I60" s="179"/>
-      <c r="J60" s="179"/>
-      <c r="O60" s="179"/>
-      <c r="P60" s="179"/>
-      <c r="Q60" s="179"/>
-      <c r="R60" s="179"/>
+      <c r="I60" s="184"/>
+      <c r="J60" s="184"/>
+      <c r="O60" s="184"/>
+      <c r="P60" s="184"/>
+      <c r="Q60" s="184"/>
+      <c r="R60" s="184"/>
     </row>
     <row r="61" spans="2:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E61" s="179"/>
-      <c r="F61" s="179"/>
+      <c r="E61" s="184"/>
+      <c r="F61" s="184"/>
       <c r="G61" s="138"/>
-      <c r="I61" s="179"/>
-      <c r="J61" s="179"/>
-      <c r="O61" s="179"/>
-      <c r="P61" s="179"/>
-      <c r="Q61" s="179"/>
-      <c r="R61" s="179"/>
+      <c r="I61" s="184"/>
+      <c r="J61" s="184"/>
+      <c r="O61" s="184"/>
+      <c r="P61" s="184"/>
+      <c r="Q61" s="184"/>
+      <c r="R61" s="184"/>
     </row>
     <row r="62" spans="2:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E62" s="179"/>
-      <c r="F62" s="179"/>
+      <c r="E62" s="184"/>
+      <c r="F62" s="184"/>
       <c r="G62" s="138"/>
-      <c r="I62" s="179"/>
-      <c r="J62" s="179"/>
-      <c r="O62" s="179"/>
-      <c r="P62" s="179"/>
-      <c r="Q62" s="179"/>
-      <c r="R62" s="179"/>
+      <c r="I62" s="184"/>
+      <c r="J62" s="184"/>
+      <c r="O62" s="184"/>
+      <c r="P62" s="184"/>
+      <c r="Q62" s="184"/>
+      <c r="R62" s="184"/>
     </row>
     <row r="63" spans="2:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E63" s="165"/>
-      <c r="F63" s="165"/>
-      <c r="I63" s="165"/>
-      <c r="J63" s="165"/>
-      <c r="O63" s="165"/>
-      <c r="P63" s="165"/>
-      <c r="Q63" s="165"/>
-      <c r="R63" s="165"/>
+      <c r="E63" s="166"/>
+      <c r="F63" s="166"/>
+      <c r="I63" s="166"/>
+      <c r="J63" s="166"/>
+      <c r="O63" s="166"/>
+      <c r="P63" s="166"/>
+      <c r="Q63" s="166"/>
+      <c r="R63" s="166"/>
     </row>
     <row r="64" spans="2:29" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E64" s="165"/>
-      <c r="F64" s="165"/>
-      <c r="I64" s="165"/>
-      <c r="J64" s="165"/>
-      <c r="O64" s="165"/>
-      <c r="P64" s="165"/>
-      <c r="Q64" s="165"/>
-      <c r="R64" s="165"/>
+      <c r="E64" s="166"/>
+      <c r="F64" s="166"/>
+      <c r="I64" s="166"/>
+      <c r="J64" s="166"/>
+      <c r="O64" s="166"/>
+      <c r="P64" s="166"/>
+      <c r="Q64" s="166"/>
+      <c r="R64" s="166"/>
     </row>
     <row r="65" spans="15:18" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="O65" s="165"/>
-      <c r="P65" s="165"/>
-      <c r="Q65" s="165"/>
-      <c r="R65" s="165"/>
+      <c r="O65" s="166"/>
+      <c r="P65" s="166"/>
+      <c r="Q65" s="166"/>
+      <c r="R65" s="166"/>
     </row>
     <row r="66" spans="15:18" x14ac:dyDescent="0.2">
-      <c r="O66" s="165"/>
-      <c r="P66" s="165"/>
-      <c r="Q66" s="165"/>
-      <c r="R66" s="165"/>
+      <c r="O66" s="166"/>
+      <c r="P66" s="166"/>
+      <c r="Q66" s="166"/>
+      <c r="R66" s="166"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="S8:T8"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="Q7:R7"/>
     <mergeCell ref="Q59:R66"/>
     <mergeCell ref="O59:P66"/>
     <mergeCell ref="E6:F6"/>
@@ -19352,6 +20089,12 @@
     <mergeCell ref="M7:N7"/>
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="I7:J7"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="S8:T8"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="Q7:R7"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0.3"/>
   <pageSetup scale="69" fitToHeight="2" orientation="portrait" r:id="rId1"/>
@@ -23672,6 +24415,522 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64F6F776-18CD-4BB0-809F-46B932C83139}">
+  <dimension ref="A1:O11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G1" t="s">
+        <v>210</v>
+      </c>
+      <c r="H1" t="s">
+        <v>220</v>
+      </c>
+      <c r="I1" t="s">
+        <v>219</v>
+      </c>
+      <c r="J1" t="s">
+        <v>218</v>
+      </c>
+      <c r="K1" t="s">
+        <v>217</v>
+      </c>
+      <c r="L1" t="s">
+        <v>216</v>
+      </c>
+      <c r="M1" t="s">
+        <v>215</v>
+      </c>
+      <c r="N1" t="s">
+        <v>214</v>
+      </c>
+      <c r="O1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B2" s="148">
+        <v>42129</v>
+      </c>
+      <c r="C2">
+        <v>2015</v>
+      </c>
+      <c r="D2">
+        <v>125</v>
+      </c>
+      <c r="E2" s="148">
+        <v>42143</v>
+      </c>
+      <c r="F2" s="148">
+        <v>42185</v>
+      </c>
+      <c r="G2" s="147">
+        <v>181.10833333333332</v>
+      </c>
+      <c r="H2" s="81">
+        <v>6.5</v>
+      </c>
+      <c r="I2" s="81">
+        <v>6</v>
+      </c>
+      <c r="J2" s="81">
+        <v>5</v>
+      </c>
+      <c r="K2" s="81">
+        <v>4.5</v>
+      </c>
+      <c r="L2" s="81">
+        <v>3.5</v>
+      </c>
+      <c r="M2" s="81">
+        <v>3.7</v>
+      </c>
+      <c r="N2" s="81">
+        <v>1.7</v>
+      </c>
+      <c r="O2" s="81">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B3" s="148">
+        <v>42129</v>
+      </c>
+      <c r="C3">
+        <v>2015</v>
+      </c>
+      <c r="D3">
+        <v>125</v>
+      </c>
+      <c r="E3" s="148">
+        <v>42143</v>
+      </c>
+      <c r="F3" s="148">
+        <v>42184</v>
+      </c>
+      <c r="G3" s="147">
+        <v>180</v>
+      </c>
+      <c r="H3" s="81">
+        <v>7.1</v>
+      </c>
+      <c r="I3" s="81">
+        <v>5.9</v>
+      </c>
+      <c r="J3" s="81">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="K3" s="81">
+        <v>5.2</v>
+      </c>
+      <c r="L3" s="81">
+        <v>4.7</v>
+      </c>
+      <c r="M3" s="81">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="N3" s="81">
+        <v>3.5</v>
+      </c>
+      <c r="O3" s="81">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B4" s="148">
+        <v>42129</v>
+      </c>
+      <c r="C4">
+        <v>2015</v>
+      </c>
+      <c r="D4">
+        <v>125</v>
+      </c>
+      <c r="E4" s="148">
+        <v>42143</v>
+      </c>
+      <c r="F4" s="148">
+        <v>42185</v>
+      </c>
+      <c r="G4" s="147">
+        <v>181.33333333333331</v>
+      </c>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81">
+        <v>5.8</v>
+      </c>
+      <c r="J4" s="81"/>
+      <c r="K4" s="81">
+        <v>4.5</v>
+      </c>
+      <c r="L4" s="81">
+        <v>4.3</v>
+      </c>
+      <c r="M4" s="81">
+        <v>4.2</v>
+      </c>
+      <c r="N4" s="81">
+        <v>2.5</v>
+      </c>
+      <c r="O4" s="81">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B5" s="148">
+        <v>42129</v>
+      </c>
+      <c r="C5">
+        <v>2015</v>
+      </c>
+      <c r="D5">
+        <v>125</v>
+      </c>
+      <c r="E5" s="148">
+        <v>42143</v>
+      </c>
+      <c r="F5" s="148">
+        <v>42184</v>
+      </c>
+      <c r="G5" s="147">
+        <v>179.93095238095239</v>
+      </c>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81">
+        <v>6</v>
+      </c>
+      <c r="J5" s="81"/>
+      <c r="K5" s="81">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="L5" s="81">
+        <v>4.5</v>
+      </c>
+      <c r="M5" s="81">
+        <v>4.3</v>
+      </c>
+      <c r="N5" s="81">
+        <v>3.3</v>
+      </c>
+      <c r="O5" s="81">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B6" s="148">
+        <v>42129</v>
+      </c>
+      <c r="C6">
+        <v>2015</v>
+      </c>
+      <c r="D6">
+        <v>125</v>
+      </c>
+      <c r="E6" s="148">
+        <v>42143</v>
+      </c>
+      <c r="F6" s="148">
+        <v>42184</v>
+      </c>
+      <c r="G6" s="147">
+        <v>180.49761904761905</v>
+      </c>
+      <c r="H6" s="81">
+        <v>6.9</v>
+      </c>
+      <c r="I6" s="81">
+        <v>6.2</v>
+      </c>
+      <c r="J6" s="81">
+        <v>4.75</v>
+      </c>
+      <c r="K6" s="81">
+        <v>4.2</v>
+      </c>
+      <c r="L6" s="81">
+        <v>3.2</v>
+      </c>
+      <c r="M6" s="81">
+        <v>2.6</v>
+      </c>
+      <c r="N6" s="81">
+        <v>1.7</v>
+      </c>
+      <c r="O6" s="81">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>231</v>
+      </c>
+      <c r="B7" s="148">
+        <v>42129</v>
+      </c>
+      <c r="C7">
+        <v>2015</v>
+      </c>
+      <c r="D7">
+        <v>125</v>
+      </c>
+      <c r="E7" s="148">
+        <v>42143</v>
+      </c>
+      <c r="F7" s="148">
+        <v>42185</v>
+      </c>
+      <c r="G7" s="147">
+        <v>180.83690476190478</v>
+      </c>
+      <c r="H7" s="81">
+        <v>7.5</v>
+      </c>
+      <c r="I7" s="81">
+        <v>5.7</v>
+      </c>
+      <c r="J7" s="81">
+        <v>5.8</v>
+      </c>
+      <c r="K7" s="81">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="L7" s="81">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="M7" s="81">
+        <v>4.7</v>
+      </c>
+      <c r="N7" s="81">
+        <v>3.6</v>
+      </c>
+      <c r="O7" s="81">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>232</v>
+      </c>
+      <c r="B8" s="148">
+        <v>42129</v>
+      </c>
+      <c r="C8">
+        <v>2015</v>
+      </c>
+      <c r="D8">
+        <v>125</v>
+      </c>
+      <c r="E8" s="148">
+        <v>42143</v>
+      </c>
+      <c r="F8" s="148">
+        <v>42185</v>
+      </c>
+      <c r="G8" s="147">
+        <v>181.405</v>
+      </c>
+      <c r="H8" s="81"/>
+      <c r="I8" s="81">
+        <v>5.9</v>
+      </c>
+      <c r="J8" s="81"/>
+      <c r="K8" s="81">
+        <v>5</v>
+      </c>
+      <c r="L8" s="81">
+        <v>4.3</v>
+      </c>
+      <c r="M8" s="81">
+        <v>4.2</v>
+      </c>
+      <c r="N8" s="81">
+        <v>3.5</v>
+      </c>
+      <c r="O8" s="81">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>233</v>
+      </c>
+      <c r="B9" s="148">
+        <v>42129</v>
+      </c>
+      <c r="C9">
+        <v>2015</v>
+      </c>
+      <c r="D9">
+        <v>125</v>
+      </c>
+      <c r="E9" s="148">
+        <v>42143</v>
+      </c>
+      <c r="F9" s="148">
+        <v>42185</v>
+      </c>
+      <c r="G9" s="147">
+        <v>181.47333333333336</v>
+      </c>
+      <c r="H9" s="81"/>
+      <c r="I9" s="81">
+        <v>6.1</v>
+      </c>
+      <c r="J9" s="81"/>
+      <c r="K9" s="81">
+        <v>4.8</v>
+      </c>
+      <c r="L9" s="81">
+        <v>4.2</v>
+      </c>
+      <c r="M9" s="81">
+        <v>4.3</v>
+      </c>
+      <c r="N9" s="81">
+        <v>3.4</v>
+      </c>
+      <c r="O9" s="81">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>234</v>
+      </c>
+      <c r="B10" s="148">
+        <v>42129</v>
+      </c>
+      <c r="C10">
+        <v>2015</v>
+      </c>
+      <c r="D10">
+        <v>125</v>
+      </c>
+      <c r="E10" s="148">
+        <v>42143</v>
+      </c>
+      <c r="F10" s="148">
+        <v>42186</v>
+      </c>
+      <c r="G10" s="147">
+        <v>182.14464285714286</v>
+      </c>
+      <c r="H10" s="81">
+        <v>6.6</v>
+      </c>
+      <c r="I10" s="81">
+        <v>6</v>
+      </c>
+      <c r="J10" s="81">
+        <v>3.75</v>
+      </c>
+      <c r="K10" s="81">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L10" s="81">
+        <v>4</v>
+      </c>
+      <c r="M10" s="81">
+        <v>4.2</v>
+      </c>
+      <c r="N10" s="81">
+        <v>3.3</v>
+      </c>
+      <c r="O10" s="81">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>239</v>
+      </c>
+      <c r="B11" s="148">
+        <v>42129</v>
+      </c>
+      <c r="C11">
+        <v>2015</v>
+      </c>
+      <c r="D11">
+        <v>125</v>
+      </c>
+      <c r="E11" s="148">
+        <v>42143</v>
+      </c>
+      <c r="F11" s="148">
+        <v>42187</v>
+      </c>
+      <c r="G11" s="147">
+        <v>183.34111111111113</v>
+      </c>
+      <c r="H11" s="81">
+        <v>7.5</v>
+      </c>
+      <c r="I11" s="81">
+        <v>6.3</v>
+      </c>
+      <c r="J11" s="81">
+        <v>5.5</v>
+      </c>
+      <c r="K11" s="81">
+        <v>3.3</v>
+      </c>
+      <c r="L11" s="81">
+        <v>2.6</v>
+      </c>
+      <c r="M11" s="81">
+        <v>2</v>
+      </c>
+      <c r="N11" s="81">
+        <v>1.7</v>
+      </c>
+      <c r="O11" s="81">
+        <v>1.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="47" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O66"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -25761,7 +27020,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AB59"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -25802,59 +27061,59 @@
       <c r="C5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="O5" s="157"/>
-      <c r="P5" s="158"/>
+      <c r="O5" s="161"/>
+      <c r="P5" s="162"/>
     </row>
     <row r="6" spans="1:28" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E6" s="164" t="s">
+      <c r="E6" s="165" t="s">
         <v>58</v>
       </c>
-      <c r="F6" s="165"/>
-      <c r="O6" s="158"/>
-      <c r="P6" s="158"/>
+      <c r="F6" s="166"/>
+      <c r="O6" s="162"/>
+      <c r="P6" s="162"/>
     </row>
     <row r="7" spans="1:28" ht="15" x14ac:dyDescent="0.25">
       <c r="D7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="159">
+      <c r="E7" s="163">
         <v>42157</v>
       </c>
-      <c r="F7" s="160"/>
-      <c r="G7" s="166">
+      <c r="F7" s="158"/>
+      <c r="G7" s="167">
         <v>42170</v>
       </c>
-      <c r="H7" s="167"/>
-      <c r="I7" s="162">
+      <c r="H7" s="168"/>
+      <c r="I7" s="159">
         <v>42184</v>
       </c>
-      <c r="J7" s="160"/>
-      <c r="K7" s="162">
+      <c r="J7" s="158"/>
+      <c r="K7" s="159">
         <v>42198</v>
       </c>
-      <c r="L7" s="160"/>
-      <c r="M7" s="162">
+      <c r="L7" s="158"/>
+      <c r="M7" s="159">
         <v>42212</v>
       </c>
-      <c r="N7" s="160"/>
-      <c r="O7" s="162">
+      <c r="N7" s="158"/>
+      <c r="O7" s="159">
         <v>42227</v>
       </c>
-      <c r="P7" s="160"/>
-      <c r="Q7" s="162">
+      <c r="P7" s="158"/>
+      <c r="Q7" s="159">
         <v>42243</v>
       </c>
-      <c r="R7" s="160"/>
-      <c r="S7" s="162">
+      <c r="R7" s="158"/>
+      <c r="S7" s="159">
         <v>42255</v>
       </c>
-      <c r="T7" s="160"/>
-      <c r="U7" s="168"/>
-      <c r="V7" s="160"/>
-      <c r="W7" s="168"/>
-      <c r="X7" s="160"/>
-      <c r="Y7" s="168"/>
-      <c r="Z7" s="160"/>
+      <c r="T7" s="158"/>
+      <c r="U7" s="157"/>
+      <c r="V7" s="158"/>
+      <c r="W7" s="157"/>
+      <c r="X7" s="158"/>
+      <c r="Y7" s="157"/>
+      <c r="Z7" s="158"/>
       <c r="AA7" s="29"/>
       <c r="AB7" s="29"/>
     </row>
@@ -25862,44 +27121,44 @@
       <c r="D8" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="161">
+      <c r="E8" s="164">
         <v>153</v>
       </c>
-      <c r="F8" s="160"/>
+      <c r="F8" s="158"/>
       <c r="G8" s="64">
         <v>166</v>
       </c>
       <c r="H8" s="64"/>
-      <c r="I8" s="168">
+      <c r="I8" s="157">
         <v>180</v>
       </c>
-      <c r="J8" s="160"/>
-      <c r="K8" s="163">
+      <c r="J8" s="158"/>
+      <c r="K8" s="160">
         <v>194</v>
       </c>
-      <c r="L8" s="160"/>
-      <c r="M8" s="163">
+      <c r="L8" s="158"/>
+      <c r="M8" s="160">
         <v>208</v>
       </c>
-      <c r="N8" s="160"/>
-      <c r="O8" s="163">
+      <c r="N8" s="158"/>
+      <c r="O8" s="160">
         <v>223</v>
       </c>
-      <c r="P8" s="160"/>
-      <c r="Q8" s="163">
+      <c r="P8" s="158"/>
+      <c r="Q8" s="160">
         <v>236</v>
       </c>
-      <c r="R8" s="160"/>
-      <c r="S8" s="163">
+      <c r="R8" s="158"/>
+      <c r="S8" s="160">
         <v>251</v>
       </c>
-      <c r="T8" s="160"/>
-      <c r="U8" s="168"/>
-      <c r="V8" s="160"/>
-      <c r="W8" s="168"/>
-      <c r="X8" s="160"/>
-      <c r="Y8" s="168"/>
-      <c r="Z8" s="160"/>
+      <c r="T8" s="158"/>
+      <c r="U8" s="157"/>
+      <c r="V8" s="158"/>
+      <c r="W8" s="157"/>
+      <c r="X8" s="158"/>
+      <c r="Y8" s="157"/>
+      <c r="Z8" s="158"/>
       <c r="AA8" s="29"/>
       <c r="AB8" s="29"/>
     </row>
@@ -29386,16 +30645,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="W7:X7"/>
-    <mergeCell ref="W8:X8"/>
-    <mergeCell ref="Y7:Z7"/>
-    <mergeCell ref="Y8:Z8"/>
-    <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="S8:T8"/>
-    <mergeCell ref="U7:V7"/>
-    <mergeCell ref="U8:V8"/>
     <mergeCell ref="O5:P6"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E8:F8"/>
@@ -29409,13 +30658,23 @@
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="I8:J8"/>
+    <mergeCell ref="W7:X7"/>
+    <mergeCell ref="W8:X8"/>
+    <mergeCell ref="Y7:Z7"/>
+    <mergeCell ref="Y8:Z8"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="S8:T8"/>
+    <mergeCell ref="U7:V7"/>
+    <mergeCell ref="U8:V8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AB66"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -29451,7 +30710,7 @@
       <c r="O3" s="155" t="s">
         <v>62</v>
       </c>
-      <c r="P3" s="173"/>
+      <c r="P3" s="169"/>
     </row>
     <row r="4" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
@@ -29459,7 +30718,7 @@
       </c>
       <c r="C4" s="4"/>
       <c r="O4" s="156"/>
-      <c r="P4" s="173"/>
+      <c r="P4" s="169"/>
     </row>
     <row r="5" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="4"/>
@@ -29467,7 +30726,7 @@
         <v>44</v>
       </c>
       <c r="O5" s="156"/>
-      <c r="P5" s="173"/>
+      <c r="P5" s="169"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C6" s="65"/>
@@ -29475,7 +30734,7 @@
         <v>45</v>
       </c>
       <c r="O6" s="156"/>
-      <c r="P6" s="173"/>
+      <c r="P6" s="169"/>
     </row>
     <row r="7" spans="1:28" ht="15" x14ac:dyDescent="0.25">
       <c r="D7" s="10" t="s">
@@ -29484,43 +30743,43 @@
       <c r="E7" s="69">
         <v>42157</v>
       </c>
-      <c r="F7" s="170" t="s">
+      <c r="F7" s="171" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="162">
+      <c r="G7" s="159">
         <v>42170</v>
       </c>
-      <c r="H7" s="160"/>
-      <c r="I7" s="162">
+      <c r="H7" s="158"/>
+      <c r="I7" s="159">
         <v>42184</v>
       </c>
-      <c r="J7" s="172"/>
-      <c r="K7" s="162">
+      <c r="J7" s="170"/>
+      <c r="K7" s="159">
         <v>42198</v>
       </c>
-      <c r="L7" s="172"/>
-      <c r="M7" s="162">
+      <c r="L7" s="170"/>
+      <c r="M7" s="159">
         <v>42212</v>
       </c>
-      <c r="N7" s="160"/>
-      <c r="O7" s="162">
+      <c r="N7" s="158"/>
+      <c r="O7" s="159">
         <v>42227</v>
       </c>
-      <c r="P7" s="160"/>
-      <c r="Q7" s="162">
+      <c r="P7" s="158"/>
+      <c r="Q7" s="159">
         <v>42243</v>
       </c>
-      <c r="R7" s="160"/>
-      <c r="S7" s="162">
+      <c r="R7" s="158"/>
+      <c r="S7" s="159">
         <v>42255</v>
       </c>
-      <c r="T7" s="160"/>
-      <c r="U7" s="168"/>
-      <c r="V7" s="160"/>
-      <c r="W7" s="168"/>
-      <c r="X7" s="160"/>
-      <c r="Y7" s="168"/>
-      <c r="Z7" s="160"/>
+      <c r="T7" s="158"/>
+      <c r="U7" s="157"/>
+      <c r="V7" s="158"/>
+      <c r="W7" s="157"/>
+      <c r="X7" s="158"/>
+      <c r="Y7" s="157"/>
+      <c r="Z7" s="158"/>
       <c r="AA7" s="29"/>
       <c r="AB7" s="29"/>
     </row>
@@ -29531,41 +30790,41 @@
       <c r="E8" s="33">
         <v>153</v>
       </c>
-      <c r="F8" s="171"/>
-      <c r="G8" s="168">
+      <c r="F8" s="172"/>
+      <c r="G8" s="157">
         <v>166</v>
       </c>
-      <c r="H8" s="160"/>
-      <c r="I8" s="168">
+      <c r="H8" s="158"/>
+      <c r="I8" s="157">
         <v>180</v>
       </c>
-      <c r="J8" s="169"/>
-      <c r="K8" s="168">
+      <c r="J8" s="173"/>
+      <c r="K8" s="157">
         <v>194</v>
       </c>
-      <c r="L8" s="169"/>
-      <c r="M8" s="163">
+      <c r="L8" s="173"/>
+      <c r="M8" s="160">
         <v>208</v>
       </c>
-      <c r="N8" s="160"/>
-      <c r="O8" s="163">
+      <c r="N8" s="158"/>
+      <c r="O8" s="160">
         <v>223</v>
       </c>
-      <c r="P8" s="160"/>
-      <c r="Q8" s="163">
+      <c r="P8" s="158"/>
+      <c r="Q8" s="160">
         <v>236</v>
       </c>
-      <c r="R8" s="160"/>
-      <c r="S8" s="163">
+      <c r="R8" s="158"/>
+      <c r="S8" s="160">
         <v>251</v>
       </c>
-      <c r="T8" s="160"/>
-      <c r="U8" s="168"/>
-      <c r="V8" s="160"/>
-      <c r="W8" s="168"/>
-      <c r="X8" s="160"/>
-      <c r="Y8" s="168"/>
-      <c r="Z8" s="160"/>
+      <c r="T8" s="158"/>
+      <c r="U8" s="157"/>
+      <c r="V8" s="158"/>
+      <c r="W8" s="157"/>
+      <c r="X8" s="158"/>
+      <c r="Y8" s="157"/>
+      <c r="Z8" s="158"/>
       <c r="AA8" s="29"/>
       <c r="AB8" s="29"/>
     </row>
@@ -32629,37 +33888,37 @@
       <c r="E65" s="69">
         <v>42157</v>
       </c>
-      <c r="F65" s="170" t="s">
+      <c r="F65" s="171" t="s">
         <v>59</v>
       </c>
-      <c r="G65" s="162">
+      <c r="G65" s="159">
         <v>42170</v>
       </c>
-      <c r="H65" s="160"/>
-      <c r="I65" s="162">
+      <c r="H65" s="158"/>
+      <c r="I65" s="159">
         <v>42184</v>
       </c>
-      <c r="J65" s="172"/>
-      <c r="K65" s="162">
+      <c r="J65" s="170"/>
+      <c r="K65" s="159">
         <v>42198</v>
       </c>
-      <c r="L65" s="172"/>
-      <c r="M65" s="162">
+      <c r="L65" s="170"/>
+      <c r="M65" s="159">
         <v>42212</v>
       </c>
-      <c r="N65" s="160"/>
-      <c r="O65" s="162">
+      <c r="N65" s="158"/>
+      <c r="O65" s="159">
         <v>42227</v>
       </c>
-      <c r="P65" s="160"/>
-      <c r="Q65" s="162">
+      <c r="P65" s="158"/>
+      <c r="Q65" s="159">
         <v>42243</v>
       </c>
-      <c r="R65" s="160"/>
-      <c r="S65" s="162">
+      <c r="R65" s="158"/>
+      <c r="S65" s="159">
         <v>42255</v>
       </c>
-      <c r="T65" s="160"/>
+      <c r="T65" s="158"/>
     </row>
     <row r="66" spans="4:20" ht="15" x14ac:dyDescent="0.25">
       <c r="D66" s="10" t="s">
@@ -32668,44 +33927,53 @@
       <c r="E66" s="33">
         <v>153</v>
       </c>
-      <c r="F66" s="171"/>
-      <c r="G66" s="168">
+      <c r="F66" s="172"/>
+      <c r="G66" s="157">
         <v>166</v>
       </c>
-      <c r="H66" s="160"/>
-      <c r="I66" s="168">
+      <c r="H66" s="158"/>
+      <c r="I66" s="157">
         <v>180</v>
       </c>
-      <c r="J66" s="169"/>
-      <c r="K66" s="168">
+      <c r="J66" s="173"/>
+      <c r="K66" s="157">
         <v>194</v>
       </c>
-      <c r="L66" s="169"/>
-      <c r="M66" s="163">
+      <c r="L66" s="173"/>
+      <c r="M66" s="160">
         <v>208</v>
       </c>
-      <c r="N66" s="160"/>
-      <c r="O66" s="163">
+      <c r="N66" s="158"/>
+      <c r="O66" s="160">
         <v>223</v>
       </c>
-      <c r="P66" s="160"/>
-      <c r="Q66" s="163">
+      <c r="P66" s="158"/>
+      <c r="Q66" s="160">
         <v>236</v>
       </c>
-      <c r="R66" s="160"/>
-      <c r="S66" s="163">
+      <c r="R66" s="158"/>
+      <c r="S66" s="160">
         <v>251</v>
       </c>
-      <c r="T66" s="160"/>
+      <c r="T66" s="158"/>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="O3:P6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="O65:P65"/>
+    <mergeCell ref="Q65:R65"/>
+    <mergeCell ref="S65:T65"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="K66:L66"/>
+    <mergeCell ref="M66:N66"/>
+    <mergeCell ref="O66:P66"/>
+    <mergeCell ref="Q66:R66"/>
+    <mergeCell ref="S66:T66"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="M65:N65"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="Y8:Z8"/>
     <mergeCell ref="Q7:R7"/>
@@ -32722,714 +33990,14 @@
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="M8:N8"/>
-    <mergeCell ref="F65:F66"/>
-    <mergeCell ref="G65:H65"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="M65:N65"/>
-    <mergeCell ref="O65:P65"/>
-    <mergeCell ref="Q65:R65"/>
-    <mergeCell ref="S65:T65"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="I66:J66"/>
-    <mergeCell ref="K66:L66"/>
-    <mergeCell ref="M66:N66"/>
-    <mergeCell ref="O66:P66"/>
-    <mergeCell ref="Q66:R66"/>
-    <mergeCell ref="S66:T66"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="O3:P6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M7:N7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:V74"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="7.42578125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" style="6" customWidth="1"/>
-    <col min="3" max="4" width="9.7109375" style="6" customWidth="1"/>
-    <col min="5" max="22" width="9.7109375" style="5" customWidth="1"/>
-    <col min="23" max="24" width="8.7109375" style="5" customWidth="1"/>
-    <col min="25" max="16384" width="8.85546875" style="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:22" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="2">
-        <v>2015</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-    </row>
-    <row r="2" spans="1:22" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-    </row>
-    <row r="3" spans="1:22" ht="18" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-    </row>
-    <row r="4" spans="1:22" ht="27" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="9"/>
-      <c r="L4" s="11"/>
-      <c r="P4" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="H5" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="12"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-    </row>
-    <row r="6" spans="1:22" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="J6" s="10"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-    </row>
-    <row r="7" spans="1:22" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="J7" s="10"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-    </row>
-    <row r="8" spans="1:22" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="C8" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="54"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="62"/>
-      <c r="G8" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="54"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="62"/>
-      <c r="K8" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="L8" s="54"/>
-      <c r="M8" s="61"/>
-      <c r="N8" s="62"/>
-      <c r="O8" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="P8" s="54"/>
-      <c r="Q8" s="61"/>
-      <c r="R8" s="62"/>
-      <c r="S8" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="T8" s="54"/>
-      <c r="U8" s="61"/>
-      <c r="V8" s="62"/>
-    </row>
-    <row r="9" spans="1:22" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="57" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="53" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="60" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="57" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" s="53" t="s">
-        <v>34</v>
-      </c>
-      <c r="J9" s="60" t="s">
-        <v>35</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="L9" s="57" t="s">
-        <v>24</v>
-      </c>
-      <c r="M9" s="53" t="s">
-        <v>34</v>
-      </c>
-      <c r="N9" s="60" t="s">
-        <v>35</v>
-      </c>
-      <c r="O9" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="P9" s="57" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q9" s="53" t="s">
-        <v>34</v>
-      </c>
-      <c r="R9" s="60" t="s">
-        <v>35</v>
-      </c>
-      <c r="S9" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="T9" s="57" t="s">
-        <v>24</v>
-      </c>
-      <c r="U9" s="53" t="s">
-        <v>34</v>
-      </c>
-      <c r="V9" s="60" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="58"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="59"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="58"/>
-      <c r="M10" s="38"/>
-      <c r="N10" s="59"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="58"/>
-      <c r="Q10" s="38"/>
-      <c r="R10" s="59"/>
-      <c r="S10" s="17"/>
-      <c r="T10" s="58"/>
-      <c r="U10" s="38"/>
-      <c r="V10" s="59"/>
-    </row>
-    <row r="11" spans="1:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="59"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="58"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="59"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="58"/>
-      <c r="Q11" s="38"/>
-      <c r="R11" s="59"/>
-      <c r="S11" s="17"/>
-      <c r="T11" s="58"/>
-      <c r="U11" s="38"/>
-      <c r="V11" s="59"/>
-    </row>
-    <row r="12" spans="1:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="59"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="58"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="59"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="58"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="59"/>
-      <c r="S12" s="17"/>
-      <c r="T12" s="58"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="59"/>
-    </row>
-    <row r="13" spans="1:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="59"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="58"/>
-      <c r="M13" s="38"/>
-      <c r="N13" s="59"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="58"/>
-      <c r="Q13" s="38"/>
-      <c r="R13" s="59"/>
-      <c r="S13" s="17"/>
-      <c r="T13" s="58"/>
-      <c r="U13" s="38"/>
-      <c r="V13" s="59"/>
-    </row>
-    <row r="14" spans="1:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="59"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="58"/>
-      <c r="M14" s="38"/>
-      <c r="N14" s="59"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="58"/>
-      <c r="Q14" s="38"/>
-      <c r="R14" s="59"/>
-      <c r="S14" s="17"/>
-      <c r="T14" s="58"/>
-      <c r="U14" s="38"/>
-      <c r="V14" s="59"/>
-    </row>
-    <row r="15" spans="1:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="58"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="59"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="58"/>
-      <c r="M15" s="38"/>
-      <c r="N15" s="59"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="58"/>
-      <c r="Q15" s="38"/>
-      <c r="R15" s="59"/>
-      <c r="S15" s="17"/>
-      <c r="T15" s="58"/>
-      <c r="U15" s="38"/>
-      <c r="V15" s="59"/>
-    </row>
-    <row r="16" spans="1:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="59"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="58"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="59"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="58"/>
-      <c r="M16" s="38"/>
-      <c r="N16" s="59"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="58"/>
-      <c r="Q16" s="38"/>
-      <c r="R16" s="59"/>
-      <c r="S16" s="17"/>
-      <c r="T16" s="58"/>
-      <c r="U16" s="38"/>
-      <c r="V16" s="59"/>
-    </row>
-    <row r="17" spans="2:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="17"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="59"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="58"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="59"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="58"/>
-      <c r="M17" s="38"/>
-      <c r="N17" s="59"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="58"/>
-      <c r="Q17" s="38"/>
-      <c r="R17" s="59"/>
-      <c r="S17" s="17"/>
-      <c r="T17" s="58"/>
-      <c r="U17" s="38"/>
-      <c r="V17" s="59"/>
-    </row>
-    <row r="18" spans="2:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="59"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="59"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="58"/>
-      <c r="M18" s="38"/>
-      <c r="N18" s="59"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="58"/>
-      <c r="Q18" s="38"/>
-      <c r="R18" s="59"/>
-      <c r="S18" s="17"/>
-      <c r="T18" s="58"/>
-      <c r="U18" s="38"/>
-      <c r="V18" s="59"/>
-    </row>
-    <row r="19" spans="2:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="59"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="58"/>
-      <c r="M19" s="38"/>
-      <c r="N19" s="59"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="58"/>
-      <c r="Q19" s="38"/>
-      <c r="R19" s="59"/>
-      <c r="S19" s="17"/>
-      <c r="T19" s="58"/>
-      <c r="U19" s="38"/>
-      <c r="V19" s="59"/>
-    </row>
-    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G20" s="55"/>
-      <c r="H20" s="55"/>
-    </row>
-    <row r="21" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G21" s="56"/>
-      <c r="H21" s="56"/>
-    </row>
-    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G22" s="56"/>
-      <c r="H22" s="56"/>
-    </row>
-    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G23" s="56"/>
-      <c r="H23" s="56"/>
-    </row>
-    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G24" s="56"/>
-      <c r="H24" s="56"/>
-    </row>
-    <row r="25" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G25" s="56"/>
-      <c r="H25" s="56"/>
-    </row>
-    <row r="26" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G26" s="56"/>
-      <c r="H26" s="56"/>
-    </row>
-    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G27" s="56"/>
-      <c r="H27" s="56"/>
-    </row>
-    <row r="28" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-    </row>
-    <row r="29" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G29" s="56"/>
-      <c r="H29" s="56"/>
-    </row>
-    <row r="30" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G30" s="56"/>
-      <c r="H30" s="56"/>
-    </row>
-    <row r="31" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G31" s="56"/>
-      <c r="H31" s="56"/>
-    </row>
-    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G32" s="56"/>
-      <c r="H32" s="56"/>
-    </row>
-    <row r="33" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G33" s="56"/>
-      <c r="H33" s="56"/>
-    </row>
-    <row r="34" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G34" s="56"/>
-      <c r="H34" s="56"/>
-    </row>
-    <row r="35" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
-    </row>
-    <row r="36" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-    </row>
-    <row r="37" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G37" s="56"/>
-      <c r="H37" s="56"/>
-    </row>
-    <row r="38" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G38" s="56"/>
-      <c r="H38" s="56"/>
-    </row>
-    <row r="39" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G39" s="56"/>
-      <c r="H39" s="56"/>
-    </row>
-    <row r="40" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G40" s="56"/>
-      <c r="H40" s="56"/>
-    </row>
-    <row r="41" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G41" s="56"/>
-      <c r="H41" s="56"/>
-    </row>
-    <row r="42" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G42" s="56"/>
-      <c r="H42" s="56"/>
-    </row>
-    <row r="43" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G43" s="56"/>
-      <c r="H43" s="56"/>
-    </row>
-    <row r="44" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G44" s="56"/>
-      <c r="H44" s="56"/>
-    </row>
-    <row r="45" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G45" s="56"/>
-      <c r="H45" s="56"/>
-    </row>
-    <row r="46" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G46" s="56"/>
-      <c r="H46" s="56"/>
-    </row>
-    <row r="47" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G47" s="56"/>
-      <c r="H47" s="56"/>
-    </row>
-    <row r="48" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G48" s="56"/>
-      <c r="H48" s="56"/>
-    </row>
-    <row r="49" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G49" s="56"/>
-      <c r="H49" s="56"/>
-    </row>
-    <row r="50" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G50" s="56"/>
-      <c r="H50" s="56"/>
-    </row>
-    <row r="51" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G51" s="56"/>
-      <c r="H51" s="56"/>
-    </row>
-    <row r="52" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G52" s="56"/>
-      <c r="H52" s="56"/>
-    </row>
-    <row r="53" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G53" s="56"/>
-      <c r="H53" s="56"/>
-    </row>
-    <row r="54" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G54" s="56"/>
-      <c r="H54" s="56"/>
-    </row>
-    <row r="55" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G55" s="56"/>
-      <c r="H55" s="56"/>
-    </row>
-    <row r="56" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G56" s="56"/>
-      <c r="H56" s="56"/>
-    </row>
-    <row r="57" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G57" s="56"/>
-      <c r="H57" s="56"/>
-    </row>
-    <row r="58" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G58" s="56"/>
-      <c r="H58" s="56"/>
-    </row>
-    <row r="59" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G59" s="56"/>
-      <c r="H59" s="56"/>
-    </row>
-    <row r="60" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G60" s="56"/>
-      <c r="H60" s="56"/>
-    </row>
-    <row r="61" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G61" s="56"/>
-      <c r="H61" s="56"/>
-    </row>
-    <row r="62" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G62" s="56"/>
-      <c r="H62" s="56"/>
-    </row>
-    <row r="63" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G63" s="56"/>
-      <c r="H63" s="56"/>
-    </row>
-    <row r="64" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G64" s="56"/>
-      <c r="H64" s="56"/>
-    </row>
-    <row r="65" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G65" s="56"/>
-      <c r="H65" s="56"/>
-    </row>
-    <row r="66" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G66" s="56"/>
-      <c r="H66" s="56"/>
-    </row>
-    <row r="67" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G67" s="56"/>
-      <c r="H67" s="56"/>
-    </row>
-    <row r="68" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G68" s="56"/>
-      <c r="H68" s="56"/>
-    </row>
-    <row r="69" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G69" s="56"/>
-      <c r="H69" s="56"/>
-    </row>
-    <row r="70" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G70" s="56"/>
-      <c r="H70" s="56"/>
-    </row>
-    <row r="71" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G71" s="56"/>
-      <c r="H71" s="56"/>
-    </row>
-    <row r="72" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G72" s="56"/>
-      <c r="H72" s="56"/>
-    </row>
-    <row r="73" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G73" s="56"/>
-      <c r="H73" s="56"/>
-    </row>
-    <row r="74" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G74" s="56"/>
-      <c r="H74" s="56"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="1" header="0.3" footer="0.53"/>
-  <pageSetup scale="63" orientation="landscape" r:id="rId1"/>
-  <headerFooter>
-    <oddFooter>&amp;R&amp;Z&amp;F
-&amp;P of &amp;N
-smm</oddFooter>
-  </headerFooter>
-</worksheet>
 </file>